--- a/Result/profitability/5201.xlsx
+++ b/Result/profitability/5201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02374999999999998</v>
+        <v>0.03499999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>41.20375</v>
+        <v>39.94125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01624999999999998</v>
+        <v>-0.1725</v>
       </c>
       <c r="N3" t="n">
-        <v>37.86625</v>
+        <v>36.01125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.13</v>
+        <v>-0.1025</v>
       </c>
       <c r="N4" t="n">
-        <v>35.82875</v>
+        <v>34.5675</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.89</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02250000000000001</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>36.37125</v>
+        <v>34.91125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.015</v>
+        <v>-0.06625000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>32.6375</v>
+        <v>31.475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04750000000000001</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>31.50375</v>
+        <v>29.28</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06125000000000001</v>
+        <v>0.00874999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>29.4675</v>
+        <v>29.87375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>61</v>
+      </c>
+      <c r="D75" t="n">
+        <v>39</v>
+      </c>
+      <c r="E75" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-41.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04499999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.83875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.835820895522388</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.250000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1022977651872836</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2501070663811563</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
